--- a/docs/po/24102026-LCMS_RATE_VERSION_UI_01_DEV_Fix_v1.1/LCMS_RATE_VERSION_UI_01_DEV_UAT_Matrix_v1.1_20261024.xlsx
+++ b/docs/po/24102026-LCMS_RATE_VERSION_UI_01_DEV_Fix_v1.1/LCMS_RATE_VERSION_UI_01_DEV_UAT_Matrix_v1.1_20261024.xlsx
@@ -998,7 +998,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>5 ảnh chụp live browser E2E layout AppShell LCMS (1366x768) trên bảng giá TDNT_SGN_HAN. Bằng chứng: screenshots/ 01 đến 05</t>
+          <t>Chụp đủ 7 ảnh Live Browser E2E AppShell Next.js (01..07) trên TDNT_SGN_HAN kết nối backend API thật, không dùng mockup HTML. Bằng chứng: thư mục screenshots/</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>RateVersionUi01FixTests.UI09_Publish_OverlappingBands_BlockedWithConflictMessage</t>
+          <t>05_rate_card_v2_publish_conflict_blocked.png, RateVersionUi01FixTests.UI09_Publish_OverlappingBands_BlockedWithConflictMessage</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>05_rate_card_v2_publish_and_version_history.png, RateVersionUi01FixTests.UI10</t>
+          <t>06_rate_card_v2_published_and_version_history.png, RateVersionUi01FixTests.UI10</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>05_rate_card_v2_publish_and_version_history.png, RateVersionUi01FixTests.UI11, UAT011</t>
+          <t>07_bill_rating_cw120_before_and_after_v2.png, RateVersionUi01FixTests.UI11, UAT011</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>05_rate_card_v2_publish_and_version_history.png, RateVersionUi01FixTests.UI12</t>
+          <t>06_rate_card_v2_published_and_version_history.png, RateVersionUi01FixTests.UI12</t>
         </is>
       </c>
     </row>

--- a/docs/po/24102026-LCMS_RATE_VERSION_UI_01_DEV_Fix_v1.1/LCMS_RATE_VERSION_UI_01_DEV_UAT_Matrix_v1.1_20261024.xlsx
+++ b/docs/po/24102026-LCMS_RATE_VERSION_UI_01_DEV_Fix_v1.1/LCMS_RATE_VERSION_UI_01_DEV_UAT_Matrix_v1.1_20261024.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản hiển thị v1 và v2 rõ ràng với trạng thái và liên kết mở xem. Bằng chứng: 05_rate_card_v2_publish_and_version_history.png</t>
+          <t>Lịch sử phiên bản hiển thị v1 và v2 rõ ràng với trạng thái và liên kết mở xem. Bằng chứng: 06_rate_card_v2_published_and_version_history.png</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Chụp đủ 7 ảnh Live Browser E2E AppShell Next.js (01..07) trên TDNT_SGN_HAN kết nối backend API thật, không dùng mockup HTML. Bằng chứng: thư mục screenshots/</t>
+          <t>Chụp đủ 8 ảnh Live Browser E2E AppShell Next.js (01..07b) trên TDNT_SGN_HAN kết nối backend API thật, không dùng mockup HTML. Bằng chứng: thư mục screenshots/</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>07_bill_rating_cw120_before_and_after_v2.png, RateVersionUi01FixTests.UI11, UAT011</t>
+          <t>07a_bill_rating_cw120_v1_no_match.png, 07b_bill_rating_cw120_v2_matched.png, 07_bill_rating_cw120_before_and_after_v2.png, RateVersionUi01FixTests.UI11, UAT011</t>
         </is>
       </c>
     </row>
